--- a/data/hex_xlsx/PIHLIS.HE.xlsx
+++ b/data/hex_xlsx/PIHLIS.HE.xlsx
@@ -13924,13 +13924,27 @@
       <c r="H160" s="21">
         <v>34.0</v>
       </c>
-      <c r="I160" s="20"/>
-      <c r="J160" s="20"/>
-      <c r="K160" s="20"/>
-      <c r="L160" s="20"/>
-      <c r="M160" s="20"/>
-      <c r="N160" s="20"/>
-      <c r="O160" s="20"/>
+      <c r="I160" s="21">
+        <v>29.72</v>
+      </c>
+      <c r="J160" s="21">
+        <v>72.15</v>
+      </c>
+      <c r="K160" s="21">
+        <v>10.78</v>
+      </c>
+      <c r="L160" s="21">
+        <v>28.68</v>
+      </c>
+      <c r="M160" s="15">
+        <v>120.88</v>
+      </c>
+      <c r="N160" s="21">
+        <v>38.09</v>
+      </c>
+      <c r="O160" s="15">
+        <v>148.19</v>
+      </c>
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
